--- a/frontend/assets/products/hutko_shop.xlsx
+++ b/frontend/assets/products/hutko_shop.xlsx
@@ -1077,7 +1077,7 @@
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>assets/products/borscht.png</t>
+          <t>assets/products/borscht.jpeg</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1173,7 +1173,7 @@
       <c r="L8" s="3" t="n"/>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>assets/products/solyanka.png</t>
+          <t>assets/products/solyanka.jpeg</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1341,7 +1341,7 @@
       <c r="L10" s="3" t="n"/>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>assets/products/zrazy.png</t>
+          <t>assets/products/zrazy.jpeg</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -1355,11 +1355,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>vegetarian</t>
-        </is>
-      </c>
+      <c r="P10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
           <t>Take zrazy straight from the freezer. | Heat a pan with oil on medium heat. | Fry 5–7 min per side until golden and heated through. | Serve with sour cream or a green salad.</t>
@@ -1388,6 +1384,11 @@
       <c r="AD10" t="inlineStr">
         <is>
           <t>Tot 6 maanden</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>assets/products/zrazy_2.jpeg,assets/products/zrazy_3.png</t>
         </is>
       </c>
     </row>
@@ -1632,6 +1633,11 @@
         </is>
       </c>
       <c r="F20" s="5" t="n"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>assets/products/borscht.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="B21" s="6" t="inlineStr">
@@ -1653,6 +1659,11 @@
         </is>
       </c>
       <c r="F21" s="6" t="n"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>assets/products/solyanka.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="B22" s="5" t="inlineStr">
@@ -1730,6 +1741,17 @@
         </is>
       </c>
       <c r="F23" s="6" t="n"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>assets/products/zrazy.jpeg</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>assets/products/zrazy_2.jpeg,assets/products/zrazy_3.png</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="B24" s="5" t="inlineStr">
@@ -1751,6 +1773,17 @@
         </is>
       </c>
       <c r="F24" s="5" t="n"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>assets/products/zrazy.jpeg</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>assets/products/zrazy_2.jpeg,assets/products/zrazy_3.png</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2444,7 +2477,7 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>assets/products/borscht.png</t>
+          <t>assets/products/borscht.jpeg</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2499,7 @@
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>assets/products/solyanka.png</t>
+          <t>assets/products/solyanka.jpeg</t>
         </is>
       </c>
     </row>
@@ -2510,7 +2543,7 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>assets/products/zrazy.png</t>
+          <t>assets/products/zrazy.jpeg</t>
         </is>
       </c>
     </row>
